--- a/analysis/TEST/RBATCH.v2.0.0.xlsx
+++ b/analysis/TEST/RBATCH.v2.0.0.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10911"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tpd0001/github/watch-wv/analysis/TEST/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6570EC-53EB-CF40-9C95-890428D41625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D549C8-CBDF-F04C-8BCC-D97138E3C00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6460" yWindow="1580" windowWidth="23220" windowHeight="14800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
-    <sheet name="Samples" sheetId="2" r:id="rId2"/>
+    <sheet name="Sample IDs" sheetId="2" r:id="rId2"/>
     <sheet name="Comments" sheetId="3" r:id="rId3"/>
-    <sheet name="Storage" sheetId="5" r:id="rId4"/>
+    <sheet name="Storage IDs" sheetId="5" r:id="rId4"/>
     <sheet name="Lists" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -391,8 +391,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -408,8 +408,8 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -418,7 +418,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -434,20 +434,16 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -867,10 +863,10 @@
       <c r="Z6" s="1"/>
     </row>
     <row r="7" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="18"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -897,10 +893,10 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="1">
         <v>10</v>
       </c>
       <c r="C8" s="1"/>
@@ -961,10 +957,10 @@
       <c r="Z9" s="1"/>
     </row>
     <row r="10" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C10" s="1"/>
@@ -1025,10 +1021,10 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="21" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="1"/>
@@ -34138,10 +34134,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C1" s="6" t="s">
@@ -34149,48 +34145,48 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="19" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="19" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="19" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="19" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="19" t="s">
         <v>52</v>
       </c>
     </row>
